--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54217886</v>
+        <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>107908</v>
+        <v>108231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,29 +1216,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skararp, Sm</t>
+          <t>Väg 534, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423037</v>
+        <v>422959</v>
       </c>
       <c r="R6" t="n">
-        <v>6277525</v>
+        <v>6278418</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1262,17 +1257,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-07-05</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-07-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>479 plantor varav 389 med blomstänglar. Ca 800 m lång sträcka längs vägen mellan Bölminge och Traryd. Lokalkoordinaten vid avtaget mot Hinneryd.</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,27 +1271,264 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>vägkant</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Leif Andersson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137366142</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137366144</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108231</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Väg 534, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>422965</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6278424</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Föryngring av slåttergubbe, östra sidan av vägen, i innerslänten</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Edvin Åhman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Leif Andersson, Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137366144</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54217886</v>
+      </c>
+      <c r="B8" t="n">
+        <v>107908</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skararp, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>423037</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6277525</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-07-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>479 plantor varav 389 med blomstänglar. Ca 800 m lång sträcka längs vägen mellan Bölminge och Traryd. Lokalkoordinaten vid avtaget mot Hinneryd.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägkant</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Bertil Möllerström</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Bertil Möllerström</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/54217886</t>
         </is>
@@ -1314,6 +1541,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108231</v>
+        <v>108234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108231</v>
+        <v>108234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108234</v>
+        <v>108240</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108234</v>
+        <v>108240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108240</v>
+        <v>108241</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108240</v>
+        <v>108241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108241</v>
+        <v>108253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108241</v>
+        <v>108253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108253</v>
+        <v>108254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108253</v>
+        <v>108254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108254</v>
+        <v>108257</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108254</v>
+        <v>108257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 625-2023 artfynd.xlsx
+++ b/artfynd/S 625-2023 artfynd.xlsx
@@ -1191,7 +1191,7 @@
         <v>137366142</v>
       </c>
       <c r="B6" t="n">
-        <v>108257</v>
+        <v>108263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>137366144</v>
       </c>
       <c r="B7" t="n">
-        <v>108257</v>
+        <v>108263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
